--- a/WB_antecedents_meta_dataset_for_github_23 June 2026.xlsx
+++ b/WB_antecedents_meta_dataset_for_github_23 June 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/k2253659/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCD1EA7-D0EB-554C-9DAE-54C9BA7FB56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CD74ED7-E4F2-024F-9FD3-2419AC93C969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="760" windowWidth="26920" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1268,7 +1268,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1280,7 +1280,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3776,7 +3775,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>5</v>
       </c>
@@ -3838,7 +3837,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
@@ -3900,7 +3899,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>36</v>
       </c>
@@ -3971,7 +3970,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>36</v>
       </c>
@@ -4042,7 +4041,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4113,7 +4112,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -4184,7 +4183,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>59</v>
       </c>
@@ -4255,7 +4254,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>59</v>
       </c>
@@ -4326,7 +4325,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>59</v>
       </c>
@@ -4397,7 +4396,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>59</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>59</v>
       </c>
@@ -4538,12 +4537,8 @@
       <c r="X43" t="s">
         <v>342</v>
       </c>
-      <c r="Y43" s="7"/>
-      <c r="Z43" s="7"/>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="7"/>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>59</v>
       </c>
@@ -4613,12 +4608,8 @@
       <c r="X44" t="s">
         <v>342</v>
       </c>
-      <c r="Y44" s="7"/>
-      <c r="Z44" s="7"/>
-      <c r="AA44" s="7"/>
-      <c r="AB44" s="7"/>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>59</v>
       </c>
@@ -4688,12 +4679,8 @@
       <c r="X45" t="s">
         <v>342</v>
       </c>
-      <c r="Y45" s="7"/>
-      <c r="Z45" s="7"/>
-      <c r="AA45" s="7"/>
-      <c r="AB45" s="7"/>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>59</v>
       </c>
@@ -4763,12 +4750,8 @@
       <c r="X46" t="s">
         <v>342</v>
       </c>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="7"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="7"/>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>59</v>
       </c>
@@ -4838,12 +4821,8 @@
       <c r="X47" t="s">
         <v>342</v>
       </c>
-      <c r="Y47" s="7"/>
-      <c r="Z47" s="7"/>
-      <c r="AA47" s="7"/>
-      <c r="AB47" s="7"/>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>59</v>
       </c>
@@ -4913,12 +4892,8 @@
       <c r="X48" t="s">
         <v>342</v>
       </c>
-      <c r="Y48" s="7"/>
-      <c r="Z48" s="7"/>
-      <c r="AA48" s="7"/>
-      <c r="AB48" s="7"/>
-    </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>59</v>
       </c>
@@ -4988,12 +4963,8 @@
       <c r="X49" t="s">
         <v>342</v>
       </c>
-      <c r="Y49" s="7"/>
-      <c r="Z49" s="7"/>
-      <c r="AA49" s="7"/>
-      <c r="AB49" s="7"/>
-    </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>59</v>
       </c>
@@ -5063,12 +5034,8 @@
       <c r="X50" t="s">
         <v>342</v>
       </c>
-      <c r="Y50" s="7"/>
-      <c r="Z50" s="7"/>
-      <c r="AA50" s="7"/>
-      <c r="AB50" s="7"/>
-    </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>67</v>
       </c>
@@ -5129,12 +5096,8 @@
       <c r="X51" t="s">
         <v>342</v>
       </c>
-      <c r="Y51" s="7"/>
-      <c r="Z51" s="7"/>
-      <c r="AA51" s="7"/>
-      <c r="AB51" s="7"/>
-    </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>67</v>
       </c>
@@ -5196,7 +5159,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>67</v>
       </c>
@@ -5258,7 +5221,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>67</v>
       </c>
@@ -5320,7 +5283,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>67</v>
       </c>
@@ -5382,7 +5345,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>67</v>
       </c>
@@ -5444,7 +5407,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>67</v>
       </c>
@@ -5506,7 +5469,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>67</v>
       </c>
@@ -5568,7 +5531,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>67</v>
       </c>
@@ -5630,7 +5593,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>67</v>
       </c>
@@ -5692,7 +5655,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>67</v>
       </c>
@@ -5754,7 +5717,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>67</v>
       </c>
@@ -5816,7 +5779,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>67</v>
       </c>
@@ -5878,7 +5841,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>67</v>
       </c>
